--- a/artfynd/A 21683-2025 artfynd.xlsx
+++ b/artfynd/A 21683-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1325,6 +1325,108 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125908991</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fula kärret, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>566273</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6516555</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21683-2025 artfynd.xlsx
+++ b/artfynd/A 21683-2025 artfynd.xlsx
@@ -1330,7 +1330,7 @@
         <v>125908991</v>
       </c>
       <c r="B8" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 21683-2025 artfynd.xlsx
+++ b/artfynd/A 21683-2025 artfynd.xlsx
@@ -1330,7 +1330,7 @@
         <v>125908991</v>
       </c>
       <c r="B8" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 21683-2025 artfynd.xlsx
+++ b/artfynd/A 21683-2025 artfynd.xlsx
@@ -1330,7 +1330,7 @@
         <v>125908991</v>
       </c>
       <c r="B8" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 21683-2025 artfynd.xlsx
+++ b/artfynd/A 21683-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1427,6 +1427,111 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127781322</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92616</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Simonstorp längs stigen, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>566258</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6516557</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21683-2025 artfynd.xlsx
+++ b/artfynd/A 21683-2025 artfynd.xlsx
@@ -1432,7 +1432,7 @@
         <v>127781322</v>
       </c>
       <c r="B9" t="n">
-        <v>92616</v>
+        <v>92622</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 21683-2025 artfynd.xlsx
+++ b/artfynd/A 21683-2025 artfynd.xlsx
@@ -1432,7 +1432,7 @@
         <v>127781322</v>
       </c>
       <c r="B9" t="n">
-        <v>92622</v>
+        <v>92625</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 21683-2025 artfynd.xlsx
+++ b/artfynd/A 21683-2025 artfynd.xlsx
@@ -1432,7 +1432,7 @@
         <v>127781322</v>
       </c>
       <c r="B9" t="n">
-        <v>92625</v>
+        <v>92633</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 21683-2025 artfynd.xlsx
+++ b/artfynd/A 21683-2025 artfynd.xlsx
@@ -1432,7 +1432,7 @@
         <v>127781322</v>
       </c>
       <c r="B9" t="n">
-        <v>92633</v>
+        <v>92634</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 21683-2025 artfynd.xlsx
+++ b/artfynd/A 21683-2025 artfynd.xlsx
@@ -1432,7 +1432,7 @@
         <v>127781322</v>
       </c>
       <c r="B9" t="n">
-        <v>92634</v>
+        <v>92635</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 21683-2025 artfynd.xlsx
+++ b/artfynd/A 21683-2025 artfynd.xlsx
@@ -1432,7 +1432,7 @@
         <v>127781322</v>
       </c>
       <c r="B9" t="n">
-        <v>92635</v>
+        <v>92636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 21683-2025 artfynd.xlsx
+++ b/artfynd/A 21683-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1532,6 +1532,200 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128311605</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92636</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>566239</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6516581</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128311606</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92642</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>566245</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6516585</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21683-2025 artfynd.xlsx
+++ b/artfynd/A 21683-2025 artfynd.xlsx
@@ -1432,7 +1432,7 @@
         <v>127781322</v>
       </c>
       <c r="B9" t="n">
-        <v>92636</v>
+        <v>92644</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>128311605</v>
       </c>
       <c r="B10" t="n">
-        <v>92636</v>
+        <v>92644</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>128311606</v>
       </c>
       <c r="B11" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 21683-2025 artfynd.xlsx
+++ b/artfynd/A 21683-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1432,7 +1432,7 @@
         <v>127781322</v>
       </c>
       <c r="B9" t="n">
-        <v>92644</v>
+        <v>92736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>128311605</v>
       </c>
       <c r="B10" t="n">
-        <v>92644</v>
+        <v>92736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>128311606</v>
       </c>
       <c r="B11" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1725,6 +1725,111 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128485886</v>
+      </c>
+      <c r="B12" t="n">
+        <v>90213</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1593</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lakritsmusseron</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tricholoma apium</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Jul.Schäff.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bredvid stigen Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>566241</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6516580</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21683-2025 artfynd.xlsx
+++ b/artfynd/A 21683-2025 artfynd.xlsx
@@ -1731,7 +1731,7 @@
         <v>128485886</v>
       </c>
       <c r="B12" t="n">
-        <v>90213</v>
+        <v>90219</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 21683-2025 artfynd.xlsx
+++ b/artfynd/A 21683-2025 artfynd.xlsx
@@ -1537,7 +1537,7 @@
         <v>128311605</v>
       </c>
       <c r="B10" t="n">
-        <v>92736</v>
+        <v>92748</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>128311606</v>
       </c>
       <c r="B11" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>128485886</v>
       </c>
       <c r="B12" t="n">
-        <v>90219</v>
+        <v>90225</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 21683-2025 artfynd.xlsx
+++ b/artfynd/A 21683-2025 artfynd.xlsx
@@ -1537,7 +1537,7 @@
         <v>128311605</v>
       </c>
       <c r="B10" t="n">
-        <v>92748</v>
+        <v>92750</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>128311606</v>
       </c>
       <c r="B11" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>128485886</v>
       </c>
       <c r="B12" t="n">
-        <v>90225</v>
+        <v>90227</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 21683-2025 artfynd.xlsx
+++ b/artfynd/A 21683-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1831,6 +1831,712 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128775253</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>566259</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6516586</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128775277</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92756</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>566254</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6516588</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128775252</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>566257</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6516586</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128775369</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>566254</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6516584</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128775257</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92784</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>566338</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6516605</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128775276</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92784</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>566235</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6516589</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128775275</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92792</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>566239</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6516587</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21683-2025 artfynd.xlsx
+++ b/artfynd/A 21683-2025 artfynd.xlsx
@@ -1537,7 +1537,7 @@
         <v>128311605</v>
       </c>
       <c r="B10" t="n">
-        <v>92750</v>
+        <v>92751</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>128311606</v>
       </c>
       <c r="B11" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,53 +1833,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128775253</v>
+        <v>128775277</v>
       </c>
       <c r="B13" t="n">
-        <v>98591</v>
+        <v>92757</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Simonstorp, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566259</v>
+        <v>566254</v>
       </c>
       <c r="R13" t="n">
-        <v>6516586</v>
+        <v>6516588</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1920,7 +1912,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1932,52 +1923,60 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128775277</v>
+        <v>128775253</v>
       </c>
       <c r="B14" t="n">
-        <v>92756</v>
+        <v>98592</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Simonstorp, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566254</v>
+        <v>566259</v>
       </c>
       <c r="R14" t="n">
-        <v>6516588</v>
+        <v>6516586</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2018,6 +2017,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Marika Sjödin, Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2039,7 +2039,7 @@
         <v>128775252</v>
       </c>
       <c r="B15" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>128775369</v>
       </c>
       <c r="B16" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>128775257</v>
       </c>
       <c r="B17" t="n">
-        <v>92784</v>
+        <v>92785</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>128775276</v>
       </c>
       <c r="B18" t="n">
-        <v>92784</v>
+        <v>92785</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>128775275</v>
       </c>
       <c r="B19" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 21683-2025 artfynd.xlsx
+++ b/artfynd/A 21683-2025 artfynd.xlsx
@@ -1731,7 +1731,7 @@
         <v>128485886</v>
       </c>
       <c r="B12" t="n">
-        <v>90227</v>
+        <v>90254</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1833,45 +1833,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128775277</v>
+        <v>128775253</v>
       </c>
       <c r="B13" t="n">
-        <v>92757</v>
+        <v>98619</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Simonstorp, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566254</v>
+        <v>566259</v>
       </c>
       <c r="R13" t="n">
-        <v>6516588</v>
+        <v>6516586</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1912,6 +1920,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1923,60 +1932,52 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Marika Sjödin, Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128775253</v>
+        <v>128775277</v>
       </c>
       <c r="B14" t="n">
-        <v>98592</v>
+        <v>92784</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Simonstorp, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566259</v>
+        <v>566254</v>
       </c>
       <c r="R14" t="n">
-        <v>6516586</v>
+        <v>6516588</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2017,7 +2018,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2039,7 +2039,7 @@
         <v>128775252</v>
       </c>
       <c r="B15" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>128775369</v>
       </c>
       <c r="B16" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>128775257</v>
       </c>
       <c r="B17" t="n">
-        <v>92785</v>
+        <v>92812</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>128775276</v>
       </c>
       <c r="B18" t="n">
-        <v>92785</v>
+        <v>92812</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>128775275</v>
       </c>
       <c r="B19" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 21683-2025 artfynd.xlsx
+++ b/artfynd/A 21683-2025 artfynd.xlsx
@@ -1537,7 +1537,7 @@
         <v>128311605</v>
       </c>
       <c r="B10" t="n">
-        <v>92751</v>
+        <v>92778</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>128311606</v>
       </c>
       <c r="B11" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,53 +1833,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128775253</v>
+        <v>128775277</v>
       </c>
       <c r="B13" t="n">
-        <v>98619</v>
+        <v>92784</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Simonstorp, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566259</v>
+        <v>566254</v>
       </c>
       <c r="R13" t="n">
-        <v>6516586</v>
+        <v>6516588</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1920,7 +1912,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1932,52 +1923,60 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128775277</v>
+        <v>128775253</v>
       </c>
       <c r="B14" t="n">
-        <v>92784</v>
+        <v>98619</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Simonstorp, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566254</v>
+        <v>566259</v>
       </c>
       <c r="R14" t="n">
-        <v>6516588</v>
+        <v>6516586</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2018,6 +2017,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Marika Sjödin, Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 21683-2025 artfynd.xlsx
+++ b/artfynd/A 21683-2025 artfynd.xlsx
@@ -1731,7 +1731,7 @@
         <v>128485886</v>
       </c>
       <c r="B12" t="n">
-        <v>90254</v>
+        <v>90259</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1833,45 +1833,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128775277</v>
+        <v>128775253</v>
       </c>
       <c r="B13" t="n">
-        <v>92784</v>
+        <v>98625</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Simonstorp, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566254</v>
+        <v>566259</v>
       </c>
       <c r="R13" t="n">
-        <v>6516588</v>
+        <v>6516586</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1912,6 +1920,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1923,60 +1932,52 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Marika Sjödin, Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128775253</v>
+        <v>128775277</v>
       </c>
       <c r="B14" t="n">
-        <v>98619</v>
+        <v>92789</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Simonstorp, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566259</v>
+        <v>566254</v>
       </c>
       <c r="R14" t="n">
-        <v>6516586</v>
+        <v>6516588</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2017,7 +2018,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2039,7 +2039,7 @@
         <v>128775252</v>
       </c>
       <c r="B15" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>128775369</v>
       </c>
       <c r="B16" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>128775257</v>
       </c>
       <c r="B17" t="n">
-        <v>92812</v>
+        <v>92817</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>128775276</v>
       </c>
       <c r="B18" t="n">
-        <v>92812</v>
+        <v>92817</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>128775275</v>
       </c>
       <c r="B19" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 21683-2025 artfynd.xlsx
+++ b/artfynd/A 21683-2025 artfynd.xlsx
@@ -1537,7 +1537,7 @@
         <v>128311605</v>
       </c>
       <c r="B10" t="n">
-        <v>92778</v>
+        <v>92788</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>128311606</v>
       </c>
       <c r="B11" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>128485886</v>
       </c>
       <c r="B12" t="n">
-        <v>90259</v>
+        <v>90264</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1833,53 +1833,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128775253</v>
+        <v>128775277</v>
       </c>
       <c r="B13" t="n">
-        <v>98625</v>
+        <v>92794</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Simonstorp, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566259</v>
+        <v>566254</v>
       </c>
       <c r="R13" t="n">
-        <v>6516586</v>
+        <v>6516588</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1920,7 +1912,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1932,52 +1923,60 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128775277</v>
+        <v>128775253</v>
       </c>
       <c r="B14" t="n">
-        <v>92789</v>
+        <v>98632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Simonstorp, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566254</v>
+        <v>566259</v>
       </c>
       <c r="R14" t="n">
-        <v>6516588</v>
+        <v>6516586</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2018,6 +2017,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Marika Sjödin, Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2039,7 +2039,7 @@
         <v>128775252</v>
       </c>
       <c r="B15" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>128775369</v>
       </c>
       <c r="B16" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>128775257</v>
       </c>
       <c r="B17" t="n">
-        <v>92817</v>
+        <v>92823</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2261,21 +2261,12 @@
       <c r="E17" t="n">
         <v>5449</v>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2345,10 +2336,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128775276</v>
+        <v>128775275</v>
       </c>
       <c r="B18" t="n">
-        <v>92817</v>
+        <v>92832</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2356,21 +2347,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2380,10 +2371,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566235</v>
+        <v>566239</v>
       </c>
       <c r="R18" t="n">
-        <v>6516589</v>
+        <v>6516587</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2442,10 +2433,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128775275</v>
+        <v>128775276</v>
       </c>
       <c r="B19" t="n">
-        <v>92825</v>
+        <v>92823</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2453,23 +2444,14 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Motaggsvamp</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2477,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566239</v>
+        <v>566235</v>
       </c>
       <c r="R19" t="n">
-        <v>6516587</v>
+        <v>6516589</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>

--- a/artfynd/A 21683-2025 artfynd.xlsx
+++ b/artfynd/A 21683-2025 artfynd.xlsx
@@ -2336,10 +2336,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128775275</v>
+        <v>128775276</v>
       </c>
       <c r="B18" t="n">
-        <v>92832</v>
+        <v>92823</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2347,23 +2347,14 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Motaggsvamp</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2371,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566239</v>
+        <v>566235</v>
       </c>
       <c r="R18" t="n">
-        <v>6516587</v>
+        <v>6516589</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2433,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128775276</v>
+        <v>128775275</v>
       </c>
       <c r="B19" t="n">
-        <v>92823</v>
+        <v>92832</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2444,14 +2435,23 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5449</v>
+        <v>5966</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566235</v>
+        <v>566239</v>
       </c>
       <c r="R19" t="n">
-        <v>6516589</v>
+        <v>6516587</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>

--- a/artfynd/A 21683-2025 artfynd.xlsx
+++ b/artfynd/A 21683-2025 artfynd.xlsx
@@ -1731,7 +1731,7 @@
         <v>128485886</v>
       </c>
       <c r="B12" t="n">
-        <v>90264</v>
+        <v>90268</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>128775277</v>
       </c>
       <c r="B13" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>128775253</v>
       </c>
       <c r="B14" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>128775252</v>
       </c>
       <c r="B15" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>128775369</v>
       </c>
       <c r="B16" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>128775257</v>
       </c>
       <c r="B17" t="n">
-        <v>92823</v>
+        <v>92827</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>128775276</v>
       </c>
       <c r="B18" t="n">
-        <v>92823</v>
+        <v>92827</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>128775275</v>
       </c>
       <c r="B19" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 21683-2025 artfynd.xlsx
+++ b/artfynd/A 21683-2025 artfynd.xlsx
@@ -2336,10 +2336,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128775276</v>
+        <v>128775275</v>
       </c>
       <c r="B18" t="n">
-        <v>92827</v>
+        <v>92836</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2347,14 +2347,23 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5449</v>
+        <v>5966</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2362,10 +2371,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566235</v>
+        <v>566239</v>
       </c>
       <c r="R18" t="n">
-        <v>6516589</v>
+        <v>6516587</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2424,10 +2433,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128775275</v>
+        <v>128775276</v>
       </c>
       <c r="B19" t="n">
-        <v>92836</v>
+        <v>92827</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2435,23 +2444,14 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Motaggsvamp</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566239</v>
+        <v>566235</v>
       </c>
       <c r="R19" t="n">
-        <v>6516587</v>
+        <v>6516589</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>

--- a/artfynd/A 21683-2025 artfynd.xlsx
+++ b/artfynd/A 21683-2025 artfynd.xlsx
@@ -1731,7 +1731,7 @@
         <v>128485886</v>
       </c>
       <c r="B12" t="n">
-        <v>90268</v>
+        <v>90273</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>128775277</v>
       </c>
       <c r="B13" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>128775253</v>
       </c>
       <c r="B14" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>128775252</v>
       </c>
       <c r="B15" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>128775369</v>
       </c>
       <c r="B16" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>128775257</v>
       </c>
       <c r="B17" t="n">
-        <v>92827</v>
+        <v>92832</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2336,10 +2336,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128775275</v>
+        <v>128775276</v>
       </c>
       <c r="B18" t="n">
-        <v>92836</v>
+        <v>92832</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2347,23 +2347,14 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Motaggsvamp</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2371,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566239</v>
+        <v>566235</v>
       </c>
       <c r="R18" t="n">
-        <v>6516587</v>
+        <v>6516589</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2433,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128775276</v>
+        <v>128775275</v>
       </c>
       <c r="B19" t="n">
-        <v>92827</v>
+        <v>92841</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2444,14 +2435,23 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5449</v>
+        <v>5966</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566235</v>
+        <v>566239</v>
       </c>
       <c r="R19" t="n">
-        <v>6516589</v>
+        <v>6516587</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>

--- a/artfynd/A 21683-2025 artfynd.xlsx
+++ b/artfynd/A 21683-2025 artfynd.xlsx
@@ -1833,53 +1833,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128775253</v>
+        <v>128775277</v>
       </c>
       <c r="B13" t="n">
-        <v>98651</v>
+        <v>92816</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Simonstorp, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566259</v>
+        <v>566254</v>
       </c>
       <c r="R13" t="n">
-        <v>6516586</v>
+        <v>6516588</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1920,7 +1912,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1932,52 +1923,60 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128775277</v>
+        <v>128775253</v>
       </c>
       <c r="B14" t="n">
-        <v>92811</v>
+        <v>98656</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Simonstorp, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566254</v>
+        <v>566259</v>
       </c>
       <c r="R14" t="n">
-        <v>6516588</v>
+        <v>6516586</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2018,6 +2017,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Marika Sjödin, Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2039,7 +2039,7 @@
         <v>128775252</v>
       </c>
       <c r="B15" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>128775369</v>
       </c>
       <c r="B16" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>128775257</v>
       </c>
       <c r="B17" t="n">
-        <v>92840</v>
+        <v>92845</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>128775276</v>
       </c>
       <c r="B18" t="n">
-        <v>92840</v>
+        <v>92845</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>128775275</v>
       </c>
       <c r="B19" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 21683-2025 artfynd.xlsx
+++ b/artfynd/A 21683-2025 artfynd.xlsx
@@ -1836,7 +1836,7 @@
         <v>128775277</v>
       </c>
       <c r="B13" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>128775253</v>
       </c>
       <c r="B14" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>128775252</v>
       </c>
       <c r="B15" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>128775369</v>
       </c>
       <c r="B16" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>128775257</v>
       </c>
       <c r="B17" t="n">
-        <v>92845</v>
+        <v>92848</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>128775276</v>
       </c>
       <c r="B18" t="n">
-        <v>92845</v>
+        <v>92848</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>128775275</v>
       </c>
       <c r="B19" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 21683-2025 artfynd.xlsx
+++ b/artfynd/A 21683-2025 artfynd.xlsx
@@ -1833,45 +1833,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128775277</v>
+        <v>128775253</v>
       </c>
       <c r="B13" t="n">
-        <v>92819</v>
+        <v>98659</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Simonstorp, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566254</v>
+        <v>566259</v>
       </c>
       <c r="R13" t="n">
-        <v>6516588</v>
+        <v>6516586</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1912,6 +1920,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1923,60 +1932,52 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Marika Sjödin, Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128775253</v>
+        <v>128775277</v>
       </c>
       <c r="B14" t="n">
-        <v>98659</v>
+        <v>92819</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Simonstorp, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566259</v>
+        <v>566254</v>
       </c>
       <c r="R14" t="n">
-        <v>6516586</v>
+        <v>6516588</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2017,7 +2018,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2336,10 +2336,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128775276</v>
+        <v>128775275</v>
       </c>
       <c r="B18" t="n">
-        <v>92848</v>
+        <v>92857</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2347,14 +2347,23 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5449</v>
+        <v>5966</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2362,10 +2371,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566235</v>
+        <v>566239</v>
       </c>
       <c r="R18" t="n">
-        <v>6516589</v>
+        <v>6516587</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2424,10 +2433,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128775275</v>
+        <v>128775276</v>
       </c>
       <c r="B19" t="n">
-        <v>92857</v>
+        <v>92848</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2435,23 +2444,14 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Motaggsvamp</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566239</v>
+        <v>566235</v>
       </c>
       <c r="R19" t="n">
-        <v>6516587</v>
+        <v>6516589</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>

--- a/artfynd/A 21683-2025 artfynd.xlsx
+++ b/artfynd/A 21683-2025 artfynd.xlsx
@@ -1836,7 +1836,7 @@
         <v>128775253</v>
       </c>
       <c r="B13" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>128775277</v>
       </c>
       <c r="B14" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>128775252</v>
       </c>
       <c r="B15" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>128775369</v>
       </c>
       <c r="B16" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>128775257</v>
       </c>
       <c r="B17" t="n">
-        <v>92848</v>
+        <v>92855</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2336,10 +2336,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128775275</v>
+        <v>128775276</v>
       </c>
       <c r="B18" t="n">
-        <v>92857</v>
+        <v>92855</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2347,23 +2347,14 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Motaggsvamp</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2371,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566239</v>
+        <v>566235</v>
       </c>
       <c r="R18" t="n">
-        <v>6516587</v>
+        <v>6516589</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2433,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128775276</v>
+        <v>128775275</v>
       </c>
       <c r="B19" t="n">
-        <v>92848</v>
+        <v>92864</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2444,14 +2435,23 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5449</v>
+        <v>5966</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566235</v>
+        <v>566239</v>
       </c>
       <c r="R19" t="n">
-        <v>6516589</v>
+        <v>6516587</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>

--- a/artfynd/A 21683-2025 artfynd.xlsx
+++ b/artfynd/A 21683-2025 artfynd.xlsx
@@ -1836,7 +1836,7 @@
         <v>128775253</v>
       </c>
       <c r="B13" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Eva Siljeholm</t>
+          <t>Eva Siljeholm, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1942,7 +1942,7 @@
         <v>128775277</v>
       </c>
       <c r="B14" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>128775252</v>
       </c>
       <c r="B15" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Eva Siljeholm</t>
+          <t>Eva Siljeholm, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2145,7 +2145,7 @@
         <v>128775369</v>
       </c>
       <c r="B16" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>128775257</v>
       </c>
       <c r="B17" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>128775276</v>
       </c>
       <c r="B18" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>128775275</v>
       </c>
       <c r="B19" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 21683-2025 artfynd.xlsx
+++ b/artfynd/A 21683-2025 artfynd.xlsx
@@ -1833,53 +1833,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128775253</v>
+        <v>128775277</v>
       </c>
       <c r="B13" t="n">
-        <v>98676</v>
+        <v>92835</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Simonstorp, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566259</v>
+        <v>566254</v>
       </c>
       <c r="R13" t="n">
-        <v>6516586</v>
+        <v>6516588</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1920,7 +1912,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1932,52 +1923,60 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Eva Siljeholm, Marika Sjödin</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128775277</v>
+        <v>128775253</v>
       </c>
       <c r="B14" t="n">
-        <v>92833</v>
+        <v>98678</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Simonstorp, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566254</v>
+        <v>566259</v>
       </c>
       <c r="R14" t="n">
-        <v>6516588</v>
+        <v>6516586</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2018,6 +2017,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Marika Sjödin, Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2039,7 +2039,7 @@
         <v>128775252</v>
       </c>
       <c r="B15" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Eva Siljeholm, Marika Sjödin</t>
+          <t>Marika Sjödin, Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2145,7 +2145,7 @@
         <v>128775369</v>
       </c>
       <c r="B16" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>128775257</v>
       </c>
       <c r="B17" t="n">
-        <v>92862</v>
+        <v>92864</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>128775276</v>
       </c>
       <c r="B18" t="n">
-        <v>92862</v>
+        <v>92864</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>128775275</v>
       </c>
       <c r="B19" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 21683-2025 artfynd.xlsx
+++ b/artfynd/A 21683-2025 artfynd.xlsx
@@ -1836,7 +1836,7 @@
         <v>128775277</v>
       </c>
       <c r="B13" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>128775253</v>
       </c>
       <c r="B14" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>128775252</v>
       </c>
       <c r="B15" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>128775369</v>
       </c>
       <c r="B16" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>128775257</v>
       </c>
       <c r="B17" t="n">
-        <v>92864</v>
+        <v>92850</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>128775276</v>
       </c>
       <c r="B18" t="n">
-        <v>92864</v>
+        <v>92850</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>128775275</v>
       </c>
       <c r="B19" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 21683-2025 artfynd.xlsx
+++ b/artfynd/A 21683-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>84035721</v>
+        <v>84035763</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566324.129573087</v>
+        <v>566227</v>
       </c>
       <c r="R2" t="n">
-        <v>6516571.87131982</v>
+        <v>6516526</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-03-31</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-03-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>84035763</v>
+        <v>118706197</v>
       </c>
       <c r="B3" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92147</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>1101</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Simonstorp västra, Ög</t>
+          <t>Simonstorp, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566226.7385793084</v>
+        <v>566253</v>
       </c>
       <c r="R3" t="n">
-        <v>6516526.13208473</v>
+        <v>6516595</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-03-31</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-03-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,27 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Amanda Sandberg, Daniel Ringlund</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>84035745</v>
+        <v>84035721</v>
       </c>
       <c r="B4" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566146.8951136868</v>
+        <v>566324</v>
       </c>
       <c r="R4" t="n">
-        <v>6516486.916626425</v>
+        <v>6516572</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2020-03-31</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-03-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,12 +969,7 @@
         <v>118703391</v>
       </c>
       <c r="B5" t="n">
-        <v>90560</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,53 +1073,55 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119459774</v>
+        <v>128485886</v>
       </c>
       <c r="B6" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>1593</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Jul.Schäff.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Simonstorp, Ög</t>
+          <t>Bredvid stigen Simonstorp, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566215</v>
+        <v>566241</v>
       </c>
       <c r="R6" t="n">
-        <v>6516535</v>
+        <v>6516580</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,12 +1145,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-31</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-31</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1207,18 +1159,19 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Daniel Ringlund</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Daniel Ringlund</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1228,12 +1181,7 @@
         <v>119459766</v>
       </c>
       <c r="B7" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,10 +1275,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125908991</v>
+        <v>128311594</v>
       </c>
       <c r="B8" t="n">
-        <v>57654</v>
+        <v>93189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,42 +1286,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fula kärret, Ög</t>
+          <t>Simonstorp, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566273</v>
+        <v>566402</v>
       </c>
       <c r="R8" t="n">
-        <v>6516555</v>
+        <v>6516622</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1397,12 +1340,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,22 +1360,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Ringlund</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Ringlund</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127781322</v>
+        <v>128311595</v>
       </c>
       <c r="B9" t="n">
-        <v>92736</v>
+        <v>93189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1440,44 +1383,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Simonstorp längs stigen, Ög</t>
+          <t>Simonstorp, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566258</v>
+        <v>566399</v>
       </c>
       <c r="R9" t="n">
-        <v>6516557</v>
+        <v>6516608</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1501,12 +1437,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1515,29 +1451,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Daniel Ringlund</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Daniel Ringlund</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128311605</v>
+        <v>128311596</v>
       </c>
       <c r="B10" t="n">
-        <v>92788</v>
+        <v>93189</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1545,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1569,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566239</v>
+        <v>566398</v>
       </c>
       <c r="R10" t="n">
-        <v>6516581</v>
+        <v>6516610</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1631,48 +1566,55 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128311606</v>
+        <v>127781322</v>
       </c>
       <c r="B11" t="n">
-        <v>92794</v>
+        <v>93191</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Simonstorp, Ög</t>
+          <t>Simonstorp längs stigen, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566245</v>
+        <v>566258</v>
       </c>
       <c r="R11" t="n">
-        <v>6516585</v>
+        <v>6516557</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1696,12 +1638,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1710,73 +1652,67 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Daniel Ringlund</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Daniel Ringlund</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128485886</v>
+        <v>128311605</v>
       </c>
       <c r="B12" t="n">
-        <v>90275</v>
+        <v>93191</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1593</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bredvid stigen Simonstorp, Ög</t>
+          <t>Simonstorp, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566241</v>
+        <v>566239</v>
       </c>
       <c r="R12" t="n">
-        <v>6516580</v>
+        <v>6516581</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1800,12 +1736,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1814,33 +1750,32 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Ringlund</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Ringlund</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128775277</v>
+        <v>128311606</v>
       </c>
       <c r="B13" t="n">
-        <v>92821</v>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1868,10 +1803,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566254</v>
+        <v>566245</v>
       </c>
       <c r="R13" t="n">
-        <v>6516588</v>
+        <v>6516585</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1898,12 +1833,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1930,53 +1865,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128775253</v>
+        <v>128775274</v>
       </c>
       <c r="B14" t="n">
-        <v>98704</v>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Simonstorp, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566259</v>
+        <v>566125</v>
       </c>
       <c r="R14" t="n">
-        <v>6516586</v>
+        <v>6516587</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2017,7 +1944,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2029,60 +1955,52 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128775252</v>
+        <v>128775277</v>
       </c>
       <c r="B15" t="n">
-        <v>98704</v>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Simonstorp, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566257</v>
+        <v>566254</v>
       </c>
       <c r="R15" t="n">
-        <v>6516586</v>
+        <v>6516588</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2123,7 +2041,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2135,60 +2052,52 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128775369</v>
+        <v>128775275</v>
       </c>
       <c r="B16" t="n">
-        <v>98704</v>
+        <v>93235</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Simonstorp, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566254</v>
+        <v>566239</v>
       </c>
       <c r="R16" t="n">
-        <v>6516584</v>
+        <v>6516587</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2229,7 +2138,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2241,46 +2149,62 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128775257</v>
+        <v>127781295</v>
       </c>
       <c r="B17" t="n">
-        <v>92850</v>
+        <v>92567</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5449</v>
+        <v>6031</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Simonstorp, Ög</t>
+          <t>Simonstorp längs stigen, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566338</v>
+        <v>566278</v>
       </c>
       <c r="R17" t="n">
-        <v>6516605</v>
+        <v>6516601</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2304,12 +2228,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2318,28 +2242,29 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Daniel Ringlund</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Daniel Ringlund</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128775276</v>
+        <v>84035745</v>
       </c>
       <c r="B18" t="n">
-        <v>92850</v>
+        <v>79084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2347,28 +2272,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5449</v>
+        <v>6446</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Simonstorp, Ög</t>
+          <t>Simonstorp västra, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566235</v>
+        <v>566147</v>
       </c>
       <c r="R18" t="n">
-        <v>6516589</v>
+        <v>6516487</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2392,12 +2326,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2020-03-31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2020-03-31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2412,22 +2346,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128775275</v>
+        <v>84035713</v>
       </c>
       <c r="B19" t="n">
-        <v>92859</v>
+        <v>79946</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2435,37 +2369,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Simonstorp, Ög</t>
+          <t>Simonstorp västra, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566239</v>
+        <v>566132</v>
       </c>
       <c r="R19" t="n">
-        <v>6516587</v>
+        <v>6516452</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2489,12 +2423,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2020-03-31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2020-03-31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2509,15 +2443,1057 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>84035714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Simonstorp västra, Ög</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>566105</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6516481</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2020-03-31</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2020-03-31</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131739036</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Fula kärret Syd, Ög</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>566135</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6516452</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Josefin Mellberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125908991</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Fula kärret, Ög</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>566273</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6516555</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125909449</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Fula kärret, Ög</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>566238</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6516519</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128775249</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>566253</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6516592</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
           <t>Marika Sjödin</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128775250</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>566250</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6516594</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
         <is>
           <t>Marika Sjödin</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128775252</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>566257</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6516586</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128775253</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>566259</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6516586</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128775369</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>566254</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6516584</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>131734936</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Fula kärret Sydväst, Ög</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>566208</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6516525</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Josefin Mellberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21683-2025 artfynd.xlsx
+++ b/artfynd/A 21683-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84035763</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118706197</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84035721</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118703391</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1175,6 +1200,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128485886</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1272,6 +1302,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119459766</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1369,6 +1404,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128311594</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1466,6 +1506,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128311595</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1563,6 +1608,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128311596</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1668,6 +1718,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127781322</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1765,6 +1820,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128311605</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1862,6 +1922,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128311606</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1959,6 +2024,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128775274</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2056,6 +2126,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128775277</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2153,6 +2228,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128775275</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2258,6 +2338,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127781295</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2355,6 +2440,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84035745</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2452,6 +2542,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84035713</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2549,6 +2644,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84035714</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2650,6 +2750,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739036</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2752,6 +2857,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125908991</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2854,6 +2964,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125909449</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2960,6 +3075,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128775249</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3066,6 +3186,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128775250</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3172,6 +3297,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128775252</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3278,6 +3408,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128775253</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3384,6 +3519,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128775369</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3494,8 +3634,43 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734936</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>